--- a/debt-legal-phases/PHASE_0_1_DEBT_LEGAL_MASTER.xlsx
+++ b/debt-legal-phases/PHASE_0_1_DEBT_LEGAL_MASTER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="547">
   <si>
     <t>Phase</t>
   </si>
@@ -51,6 +51,342 @@
     <t>Backfill Logic</t>
   </si>
   <si>
+    <t>0/1</t>
+  </si>
+  <si>
+    <t>ALTER</t>
+  </si>
+  <si>
+    <t>Billing_Section129LetterOFDemand</t>
+  </si>
+  <si>
+    <t>IncludePensioners</t>
+  </si>
+  <si>
+    <t>BIT</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>DF_Section129_IncludePensioners</t>
+  </si>
+  <si>
+    <t>Flag to include pensioner accounts in S129 run</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>SET=0 for all existing rows</t>
+  </si>
+  <si>
+    <t>WhatsApp</t>
+  </si>
+  <si>
+    <t>DF_Section129_WhatsApp</t>
+  </si>
+  <si>
+    <t>Flag to enable WhatsApp notice distribution</t>
+  </si>
+  <si>
+    <t>StatusID</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>DF_Section129_StatusID</t>
+  </si>
+  <si>
+    <t>Unified status tracking: 0=Draft, 1=TrialRunning, 2=TrialComplete, 3=UnderReview, 4=Approved, 6=FinalRunning, 7=FinalComplete</t>
+  </si>
+  <si>
+    <t>IX_S129_StatusID</t>
+  </si>
+  <si>
+    <t>SET=0 (DRAFT) for all existing rows</t>
+  </si>
+  <si>
+    <t>Billing_Section129LetterOFDemandDetails</t>
+  </si>
+  <si>
+    <t>Selected</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>DF_Section129Details_Selected</t>
+  </si>
+  <si>
+    <t>Reviewer can select/deselect accounts during trial review</t>
+  </si>
+  <si>
+    <t>SET=1 for all existing rows</t>
+  </si>
+  <si>
+    <t>CREATE</t>
+  </si>
+  <si>
+    <t>Billing_Section129RunFiles</t>
+  </si>
+  <si>
+    <t>RunFileID (PK)</t>
+  </si>
+  <si>
+    <t>INT IDENTITY(1,1)</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>PK_Section129RunFiles</t>
+  </si>
+  <si>
+    <t>Tracks generated files (PDF, XLSX, ZIP) per S129 run</t>
+  </si>
+  <si>
+    <t>IX_RunFiles_RunID</t>
+  </si>
+  <si>
+    <t>RunID (FK)</t>
+  </si>
+  <si>
+    <t>FK → Billing_Section129LetterOFDemand.ID</t>
+  </si>
+  <si>
+    <t>Links file to parent S129 run</t>
+  </si>
+  <si>
+    <t>FileName</t>
+  </si>
+  <si>
+    <t>NVARCHAR(500)</t>
+  </si>
+  <si>
+    <t>Original file name</t>
+  </si>
+  <si>
+    <t>FileType</t>
+  </si>
+  <si>
+    <t>NVARCHAR(20)</t>
+  </si>
+  <si>
+    <t>PDF, XLSX, ZIP, CSV</t>
+  </si>
+  <si>
+    <t>FileSizeKB</t>
+  </si>
+  <si>
+    <t>File size in KB</t>
+  </si>
+  <si>
+    <t>FilePath</t>
+  </si>
+  <si>
+    <t>NVARCHAR(1000)</t>
+  </si>
+  <si>
+    <t>Server-side storage path</t>
+  </si>
+  <si>
+    <t>DateCreated</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>GETDATE()</t>
+  </si>
+  <si>
+    <t>DF_RunFiles_DateCreated</t>
+  </si>
+  <si>
+    <t>Auto-set on insert</t>
+  </si>
+  <si>
+    <t>CreatedBy</t>
+  </si>
+  <si>
+    <t>User who generated the file</t>
+  </si>
+  <si>
+    <t>Billing_Section129Config</t>
+  </si>
+  <si>
+    <t>ConfigID (PK)</t>
+  </si>
+  <si>
+    <t>PK_Section129Config</t>
+  </si>
+  <si>
+    <t>Per-FY configuration for Section 129 process</t>
+  </si>
+  <si>
+    <t>UQ_Config_FinYear (unique)</t>
+  </si>
+  <si>
+    <t>FinYear</t>
+  </si>
+  <si>
+    <t>UQ_Config_FinYear</t>
+  </si>
+  <si>
+    <t>Financial year e.g. 2025/2026. Only ONE config per FY.</t>
+  </si>
+  <si>
+    <t>Section129TemplateID</t>
+  </si>
+  <si>
+    <t>FK → Billing_LetterTemplates</t>
+  </si>
+  <si>
+    <t>Reference to demand letter template</t>
+  </si>
+  <si>
+    <t>SmsTemplateID</t>
+  </si>
+  <si>
+    <t>Reference to SMS template</t>
+  </si>
+  <si>
+    <t>LapseDays</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>DF_Config_LapseDays</t>
+  </si>
+  <si>
+    <t>Workdays before notice lapses (default 14, excludes weekends/holidays)</t>
+  </si>
+  <si>
+    <t>NoticesPerFile</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Max notices per generated PDF file</t>
+  </si>
+  <si>
+    <t>ActivateRotation</t>
+  </si>
+  <si>
+    <t>Enable attorney rotation for auto-handover after lapse</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Whether this config is active</t>
+  </si>
+  <si>
+    <t>CapturerID / DateCaptured / ModifierID / DateModified</t>
+  </si>
+  <si>
+    <t>INT / DATETIME</t>
+  </si>
+  <si>
+    <t>Standard audit fields — who created/modified and when</t>
+  </si>
+  <si>
+    <t>Billing_Section129ConfigCostItems</t>
+  </si>
+  <si>
+    <t>CostItemID (PK)</t>
+  </si>
+  <si>
+    <t>PK_ConfigCostItems</t>
+  </si>
+  <si>
+    <t>Fee line items per S129 config (Admin Fee, Postage, etc.)</t>
+  </si>
+  <si>
+    <t>IX_CostItems_ConfigID</t>
+  </si>
+  <si>
+    <t>ConfigID (FK)</t>
+  </si>
+  <si>
+    <t>FK → Billing_Section129Config.ConfigID</t>
+  </si>
+  <si>
+    <t>Links cost item to parent config</t>
+  </si>
+  <si>
+    <t>CostDescription</t>
+  </si>
+  <si>
+    <t>NVARCHAR(200)</t>
+  </si>
+  <si>
+    <t>Human-readable name (e.g. "Admin Fee", "Postage Fee")</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>DECIMAL(18,2)</t>
+  </si>
+  <si>
+    <t>Fee amount in ZAR Rands</t>
+  </si>
+  <si>
+    <t>IsActive</t>
+  </si>
+  <si>
+    <t>Whether this cost item is currently active</t>
+  </si>
+  <si>
+    <t>Billing_Section129ConfigAttorneyRotation</t>
+  </si>
+  <si>
+    <t>RotationID (PK)</t>
+  </si>
+  <si>
+    <t>PK_ConfigAttorneyRotation</t>
+  </si>
+  <si>
+    <t>Attorney allocation % for rotation-based handover after lapse</t>
+  </si>
+  <si>
+    <t>IX_Rotation_ConfigID</t>
+  </si>
+  <si>
+    <t>Links rotation to parent config</t>
+  </si>
+  <si>
+    <t>AttorneyID (FK)</t>
+  </si>
+  <si>
+    <t>FK → Const_Attorney.ID</t>
+  </si>
+  <si>
+    <t>Reference to attorney master data</t>
+  </si>
+  <si>
+    <t>Commission</t>
+  </si>
+  <si>
+    <t>DECIMAL(5,2)</t>
+  </si>
+  <si>
+    <t>Percentage allocation — all active rotations per config must total 100%</t>
+  </si>
+  <si>
+    <t>Whether this attorney is in active rotation</t>
+  </si>
+  <si>
     <t>API ID</t>
   </si>
   <si>
@@ -84,6 +420,537 @@
     <t>Notes / Business Rules</t>
   </si>
   <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>Lookups</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/billing-cycles</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/billing-cycles</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>[ { id: number, name: string } ]</t>
+  </si>
+  <si>
+    <t>Section129NoticesComponent, Section129ConfigComponent</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/billing-cycles")</t>
+  </si>
+  <si>
+    <t>Dropdown source for billing cycle filter. Reads from Billing_BillingCycles table.</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/towns</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/towns</t>
+  </si>
+  <si>
+    <t>Section129NoticesComponent</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/towns")</t>
+  </si>
+  <si>
+    <t>Dropdown source for town filter. Reads from Const_Town table.</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/property-categories</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/property-categories</t>
+  </si>
+  <si>
+    <t>Section129NoticesComponent, QualificationRulesComponent</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/property-categories")</t>
+  </si>
+  <si>
+    <t>Property category dropdown. Reads from Const_PropertyCategory.</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/account-types</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/account-types</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/account-types")</t>
+  </si>
+  <si>
+    <t>Account type dropdown. Reads from Const_AccountType.</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/person-types</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/person-types</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/person-types")</t>
+  </si>
+  <si>
+    <t>Person type dropdown. Reads from Const_TypeOfPerson.</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/ageing-ranges</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/ageing-ranges</t>
+  </si>
+  <si>
+    <t>[ { id: number, name: string, daysFrom: number, daysTo: number } ]</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/ageing-ranges")</t>
+  </si>
+  <si>
+    <t>Outstanding period / ageing dropdown. Reads from Const_OutstandingPeriod.</t>
+  </si>
+  <si>
+    <t>L7</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/attorney-list</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/attorney-list</t>
+  </si>
+  <si>
+    <t>[ { id: number, name: string, contactNo: string, email: string, commission: number } ]</t>
+  </si>
+  <si>
+    <t>Section129ConfigComponent, HandoverManagementComponent</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/attorney-list")</t>
+  </si>
+  <si>
+    <t>Attorney master data for rotation config and handover. Reads from Const_Attorney.</t>
+  </si>
+  <si>
+    <t>L8</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-templates</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-templates</t>
+  </si>
+  <si>
+    <t>[ { id: number, name: string, templateType: string } ]</t>
+  </si>
+  <si>
+    <t>Section129ConfigComponent</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-templates")</t>
+  </si>
+  <si>
+    <t>Document templates for S129 letter generation. Reads from Billing_LetterTemplates.</t>
+  </si>
+  <si>
+    <t>L9</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-sms-templates</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-sms-templates</t>
+  </si>
+  <si>
+    <t>[ { id: number, name: string, content: string } ]</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-sms-templates")</t>
+  </si>
+  <si>
+    <t>SMS templates for S129 notifications.</t>
+  </si>
+  <si>
+    <t>L10</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/additional-billing-types</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/additional-billing-types</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/additional-billing-types")</t>
+  </si>
+  <si>
+    <t>Additional billing type lookups.</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>S129 Config</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-config</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-config</t>
+  </si>
+  <si>
+    <t>finYear=2025/2026</t>
+  </si>
+  <si>
+    <t>{ id, finYear, section129TemplateId, smsTemplateId, lapseDays, noticesPerFile, activateRotation, enabled, costItems: [{costItemId, costDescription, amount, isActive}], attorneyRotation: [{rotationId, attorneyId, attorneyName, commission, isActive}] }</t>
+  </si>
+  <si>
+    <t>Section129ConfigComponent (/debt/section129/config)</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-config", {finYear})</t>
+  </si>
+  <si>
+    <t>Returns active config for given FY. Rule: Only ONE config per FY allowed. Reads from Billing_Section129Config + CostItems + AttorneyRotation.</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-config-list</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-config-list</t>
+  </si>
+  <si>
+    <t>[ { id, finYear, enabled, lapseDays, section129TemplateId, activateRotation } ]</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-config-list")</t>
+  </si>
+  <si>
+    <t>List all configs across FYs for management grid.</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-config-save</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-config-save</t>
+  </si>
+  <si>
+    <t>{ id?, finYear, section129TemplateId, smsTemplateId, lapseDays, noticesPerFile, activateRotation, enabled, costItems: [{costDescription, amount, isActive}], attorneyRotation: [{attorneyId, commission, isActive}], capturerID, dateCaptured, modifierID, dateModified }</t>
+  </si>
+  <si>
+    <t>{ success: boolean, id: number, message?: string }</t>
+  </si>
+  <si>
+    <t>api.post("/api/platinum/billing-debt/section129-config-save", body)</t>
+  </si>
+  <si>
+    <t>Upsert (create or update). Attorney rotation commission% MUST total 100%. Audit fields injected by Express middleware.</t>
+  </si>
+  <si>
+    <t>N1</t>
+  </si>
+  <si>
+    <t>S129 Notices</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-runs</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-runs</t>
+  </si>
+  <si>
+    <t>finYear=2025/2026&amp;finMonth=1</t>
+  </si>
+  <si>
+    <t>[ { id, statusId, statusDescription, runDate, runType, billingCycleId, totalAccounts, totalAmount, createdBy, createdDate } ]</t>
+  </si>
+  <si>
+    <t>Section129NoticesComponent (/debt/section129)</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-runs", {finYear, finMonth})</t>
+  </si>
+  <si>
+    <t>Lists all S129 runs for given FY/month. StatusID maps to lifecycle: 0=Draft, 1=TrialRunning, 2=TrialComplete, 3=UnderReview, 4=Approved, 6=FinalRunning, 7=FinalComplete.</t>
+  </si>
+  <si>
+    <t>N2</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-trial-run</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-trial-run</t>
+  </si>
+  <si>
+    <t>{ finYear, finMonth, runType, billingCycleId, handoverOption, distributionType, townId?, ageing?, amountGreaterThan?, includeIndigents?, includePensioners?, propertyCategories?: number[], accountTypes?: number[], personTypes?: number[], capturerID, dateCaptured, modifierID, dateModified }</t>
+  </si>
+  <si>
+    <t>{ success: boolean, runId: number, message?: string }</t>
+  </si>
+  <si>
+    <t>api.post("/api/platinum/billing-debt/section129-trial-run", body)</t>
+  </si>
+  <si>
+    <t>Creates run header (StatusID=1 TRIAL_RUNNING). Backend: INSERT into Billing_Section129LetterOFDemand then publish StartSection129TrialRun message to Azure Service Bus queue. Worker identifies qualifying accounts and writes to Details table. Frontend polls N10 every 5s for completion.</t>
+  </si>
+  <si>
+    <t>N3</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-run-accounts</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-run-accounts</t>
+  </si>
+  <si>
+    <t>runId=123&amp;page=1&amp;pageSize=50</t>
+  </si>
+  <si>
+    <t>{ accounts: [{ detailId, accountNo, accountName, totalBalance, currentBalance, balanceDue, thirtyDays, sixtyDays, ninetyDays, overNinety, selected }], totalCount: number, totalAmount: number }</t>
+  </si>
+  <si>
+    <t>Section129TrialReviewComponent (/debt/section129/review/:runId)</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-run-accounts", {runId, page, pageSize})</t>
+  </si>
+  <si>
+    <t>Returns paginated account list for a run from Billing_Section129LetterOFDemandDetails. Supports search by accountNo/name. Selected column shows reviewer selections.</t>
+  </si>
+  <si>
+    <t>N4</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-trial-review-submit</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-trial-review-submit</t>
+  </si>
+  <si>
+    <t>{ runId: number, selectedAccountIds: number[], deselectedAccountIds: number[], isFinalReviewComplete: boolean, isReview: true, capturerID, dateCaptured, modifierID, dateModified }</t>
+  </si>
+  <si>
+    <t>{ success: boolean, message?: string }</t>
+  </si>
+  <si>
+    <t>Section129TrialReviewComponent</t>
+  </si>
+  <si>
+    <t>api.post("/api/platinum/billing-debt/section129-trial-review-submit", body)</t>
+  </si>
+  <si>
+    <t>Updates Selected column on Details table. Sets header StatusID=3 (UNDER_REVIEW) when isFinalReviewComplete=true. isReview flag injected by Express middleware.</t>
+  </si>
+  <si>
+    <t>N5</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-authorize</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-authorize</t>
+  </si>
+  <si>
+    <t>{ runId: number, decision: "Approve"|"Decline", notes?: string, isReview: true, capturerID, dateCaptured, modifierID, dateModified }</t>
+  </si>
+  <si>
+    <t>Section129AuthorizationComponent (/debt/section129/authorize)</t>
+  </si>
+  <si>
+    <t>api.post("/api/platinum/billing-debt/section129-authorize", body)</t>
+  </si>
+  <si>
+    <t>Supervisor approves or declines reviewed run. Approve sets StatusID=4. Decline sets StatusID=2 (returns to review). Requires supervisor role.</t>
+  </si>
+  <si>
+    <t>N6</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-final-run</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-final-run</t>
+  </si>
+  <si>
+    <t>{ runId: number, capturerID, dateCaptured, modifierID, dateModified }</t>
+  </si>
+  <si>
+    <t>Section129AuthorizationComponent</t>
+  </si>
+  <si>
+    <t>api.post("/api/platinum/billing-debt/section129-final-run", body)</t>
+  </si>
+  <si>
+    <t>Triggers final notice generation. Sets StatusID=6 (FINAL_RUNNING). Publishes to Service Bus. Worker generates PDF letters, SMS messages, writes to RunFiles table. Poll N10 for completion. Only allowed when StatusID=4 (Approved).</t>
+  </si>
+  <si>
+    <t>N7</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-run-files</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-run-files</t>
+  </si>
+  <si>
+    <t>runId=123</t>
+  </si>
+  <si>
+    <t>[ { runFileId, fileName, fileType, fileSizeKB, dateCreated, createdBy } ]</t>
+  </si>
+  <si>
+    <t>Section129NoticesComponent, Section129ReportComponent</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-run-files", {runId})</t>
+  </si>
+  <si>
+    <t>Lists generated files after final run completes (StatusID=7). Reads from Billing_Section129RunFiles.</t>
+  </si>
+  <si>
+    <t>N8</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-download-file</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-download-file</t>
+  </si>
+  <si>
+    <t>runFileId=456</t>
+  </si>
+  <si>
+    <t>Binary file stream (application/pdf, application/zip)</t>
+  </si>
+  <si>
+    <t>window.open("/api/platinum/billing-debt/section129-download-file?runFileId=456")</t>
+  </si>
+  <si>
+    <t>Downloads a specific generated file. Returns binary stream with Content-Disposition header.</t>
+  </si>
+  <si>
+    <t>N9</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-delete-run</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-delete-run</t>
+  </si>
+  <si>
+    <t>api.post("/api/platinum/billing-debt/section129-delete-run", body)</t>
+  </si>
+  <si>
+    <t>Soft-deletes a DRAFT run. Only allowed when StatusID=0. Should NOT delete runs in any other status.</t>
+  </si>
+  <si>
+    <t>N10</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-run-status</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-run-status</t>
+  </si>
+  <si>
+    <t>{ runId, statusId, statusDescription, progress?, completedAccounts?, totalAccounts?, errors?: string[] }</t>
+  </si>
+  <si>
+    <t>Section129NoticesComponent (polling)</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-run-status", {runId})</t>
+  </si>
+  <si>
+    <t>Polling endpoint. Frontend polls every 5s while StatusID=1 (trial) or 6 (final). Stops when StatusID=2 (trial complete) or 7 (final complete). Returns progress percentage.</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>S129 Reports</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/section129-report</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/section129-report</t>
+  </si>
+  <si>
+    <t>finYear=2025/2026&amp;dateFrom=2025-07-01&amp;dateTo=2026-01-31&amp;townId?&amp;statusId?</t>
+  </si>
+  <si>
+    <t>[ { runId, runDate, statusDescription, totalAccounts, totalAmount, filesGenerated, townName } ]</t>
+  </si>
+  <si>
+    <t>Section129ReportComponent (/debt/section129-report)</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/section129-report", params)</t>
+  </si>
+  <si>
+    <t>Filterable report grid. Supports date range, town, status filters. Aggregated query across runs.</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>/api/BillingDebt/sms-log-report</t>
+  </si>
+  <si>
+    <t>/api/platinum/billing-debt/sms-log-report</t>
+  </si>
+  <si>
+    <t>finYear=2025/2026&amp;dateFrom?&amp;dateTo?&amp;status?</t>
+  </si>
+  <si>
+    <t>[ { smsId, accountNo, mobileNo, message, status, sentDate, deliveredDate, failReason? } ]</t>
+  </si>
+  <si>
+    <t>SmsLogReportComponent (/debt/sms-log-report)</t>
+  </si>
+  <si>
+    <t>api.get("/api/platinum/billing-debt/sms-log-report", params)</t>
+  </si>
+  <si>
+    <t>SMS delivery log for S129 notifications. Statuses: Pending, Sent, Delivered, Failed.</t>
+  </si>
+  <si>
     <t>Angular Route</t>
   </si>
   <si>
@@ -105,6 +972,102 @@
     <t>Status</t>
   </si>
   <si>
+    <t>/debt/section129</t>
+  </si>
+  <si>
+    <t>features/debt/section129/section129-notices.component.ts</t>
+  </si>
+  <si>
+    <t>L1-L6, N1, N2, N9, N10, N7, N8</t>
+  </si>
+  <si>
+    <t>billing-cycles, towns, property-categories, account-types, person-types, ageing-ranges, section129-runs, section129-trial-run, section129-delete-run, section129-run-status, section129-run-files, section129-download-file</t>
+  </si>
+  <si>
+    <t>Run listing grid, trial run form with filter dropdowns, status polling with progress bar, file download links, delete draft runs</t>
+  </si>
+  <si>
+    <t>Built — pending API</t>
+  </si>
+  <si>
+    <t>/debt/section129/review/:runId</t>
+  </si>
+  <si>
+    <t>features/debt/section129/section129-trial-review.component.ts</t>
+  </si>
+  <si>
+    <t>N3, N4</t>
+  </si>
+  <si>
+    <t>section129-run-accounts, section129-trial-review-submit</t>
+  </si>
+  <si>
+    <t>Paginated account grid with select/deselect checkboxes, bulk select all, search by account/name, submit review</t>
+  </si>
+  <si>
+    <t>/debt/section129/authorize</t>
+  </si>
+  <si>
+    <t>features/debt/section129/section129-authorization.component.ts</t>
+  </si>
+  <si>
+    <t>N1, N5, N6</t>
+  </si>
+  <si>
+    <t>section129-runs (status=3), section129-authorize, section129-final-run</t>
+  </si>
+  <si>
+    <t>List runs awaiting authorization (StatusID=3), approve/decline with notes field, trigger final run button</t>
+  </si>
+  <si>
+    <t>/debt/section129/config</t>
+  </si>
+  <si>
+    <t>features/debt/section129/section129-config.component.ts</t>
+  </si>
+  <si>
+    <t>C1, C2, C3, L7, L8, L9</t>
+  </si>
+  <si>
+    <t>section129-config, section129-config-list, section129-config-save, attorney-list, section129-templates, section129-sms-templates</t>
+  </si>
+  <si>
+    <t>Per-FY config management form, cost items inline CRUD table, attorney rotation % table (must total 100%), template dropdowns</t>
+  </si>
+  <si>
+    <t>/debt/section129-report</t>
+  </si>
+  <si>
+    <t>Section129ReportComponent</t>
+  </si>
+  <si>
+    <t>features/debt/section129/section129-report.component.ts</t>
+  </si>
+  <si>
+    <t>R1, N7, N8</t>
+  </si>
+  <si>
+    <t>section129-report, section129-run-files, section129-download-file</t>
+  </si>
+  <si>
+    <t>Report grid with date range + town + status filters, drill-down to run files, PDF/ZIP download</t>
+  </si>
+  <si>
+    <t>/debt/sms-log-report</t>
+  </si>
+  <si>
+    <t>SmsLogReportComponent</t>
+  </si>
+  <si>
+    <t>features/debt/communication/sms-log-report.component.ts</t>
+  </si>
+  <si>
+    <t>sms-log-report</t>
+  </si>
+  <si>
+    <t>SMS delivery log with status/date filters, export to Excel/CSV</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
@@ -123,6 +1086,231 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>Run ALTER TABLE on Billing_Section129LetterOFDemand — add IncludePensioners (BIT, default 0), WhatsApp (BIT, default 0), StatusID (INT, default 0)</t>
+  </si>
+  <si>
+    <t>DBA</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>SQL script in PHASE1_V2_DB_CHANGE_SCRIPT.sql. Idempotent — safe to re-run.</t>
+  </si>
+  <si>
+    <t>Run ALTER TABLE on Billing_Section129LetterOFDemandDetails — add Selected (BIT, default 1)</t>
+  </si>
+  <si>
+    <t>Must run before trial review API (N4) works.</t>
+  </si>
+  <si>
+    <t>CREATE TABLE Billing_Section129RunFiles (RunFileID PK, RunID FK, FileName, FileType, FileSizeKB, FilePath, DateCreated, CreatedBy)</t>
+  </si>
+  <si>
+    <t>Required for file tracking after final run.</t>
+  </si>
+  <si>
+    <t>CREATE TABLE Billing_Section129Config + Billing_Section129ConfigCostItems + Billing_Section129ConfigAttorneyRotation</t>
+  </si>
+  <si>
+    <t>All 3 tables must be created together. Config has unique constraint on FinYear.</t>
+  </si>
+  <si>
+    <t>CREATE INDEXES: IX_S129_StatusID, IX_RunFiles_RunID, IX_CostItems_ConfigID, IX_Rotation_ConfigID, UQ_Config_FinYear, IX_S129Detail_Selected</t>
+  </si>
+  <si>
+    <t>Performance optimization. Can run after tables are created.</t>
+  </si>
+  <si>
+    <t>Backfill existing rows: StatusID=0 on LetterOFDemand, Selected=1 on Details, IncludePensioners=0, WhatsApp=0</t>
+  </si>
+  <si>
+    <t>Safe — defaults preserve existing behavior. Run after ALTERs.</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Create BillingDebt controller on Platinum API project (new controller class)</t>
+  </si>
+  <si>
+    <t>API Team</t>
+  </si>
+  <si>
+    <t>New controller at /api/BillingDebt/ — all debt/legal endpoints live here.</t>
+  </si>
+  <si>
+    <t>Implement 10 lookup endpoints (L1-L10): billing-cycles, towns, property-categories, account-types, person-types, ageing-ranges, attorney-list, section129-templates, section129-sms-templates, additional-billing-types</t>
+  </si>
+  <si>
+    <t>Simple SELECT queries from existing lookup tables. All return [{id, name}] arrays.</t>
+  </si>
+  <si>
+    <t>Implement section129-config GET (C1) — return config + nested costItems[] + attorneyRotation[] for a finYear</t>
+  </si>
+  <si>
+    <t>JOIN across Config + CostItems + AttorneyRotation. Only ONE active config per FY.</t>
+  </si>
+  <si>
+    <t>Implement section129-config-list GET (C2) — list all configs</t>
+  </si>
+  <si>
+    <t>Simple SELECT from Config table.</t>
+  </si>
+  <si>
+    <t>Implement section129-config-save POST (C3) — upsert config with nested cost items and attorney rotation</t>
+  </si>
+  <si>
+    <t>Must validate: attorney rotation commission% totals 100%. Use transaction for parent + children inserts.</t>
+  </si>
+  <si>
+    <t>Implement section129-runs GET (N1) — list runs for finYear/finMonth</t>
+  </si>
+  <si>
+    <t>SELECT from Billing_Section129LetterOFDemand with StatusID description mapping.</t>
+  </si>
+  <si>
+    <t>Implement section129-trial-run POST (N2) — create run header + publish to Service Bus</t>
+  </si>
+  <si>
+    <t>INSERT header with StatusID=1. Publish StartSection129TrialRun message to Azure Service Bus queue.</t>
+  </si>
+  <si>
+    <t>Implement section129-run-accounts GET (N3) — paginated account list for a run</t>
+  </si>
+  <si>
+    <t>Paginated SELECT from Details table. Support search by accountNo/name.</t>
+  </si>
+  <si>
+    <t>Implement section129-trial-review-submit POST (N4) — update Selected column on details</t>
+  </si>
+  <si>
+    <t>Batch UPDATE Selected column. Set header StatusID=3 when isFinalReviewComplete=true.</t>
+  </si>
+  <si>
+    <t>Implement section129-authorize POST (N5) — approve/decline run</t>
+  </si>
+  <si>
+    <t>UPDATE StatusID on header. Approve→4, Decline→2. Record reviewer notes.</t>
+  </si>
+  <si>
+    <t>Implement section129-final-run POST (N6) — trigger final generation via Service Bus</t>
+  </si>
+  <si>
+    <t>Set StatusID=6, publish to Service Bus. Worker generates PDFs and writes to RunFiles table.</t>
+  </si>
+  <si>
+    <t>Implement section129-run-files GET (N7) + section129-download-file GET (N8)</t>
+  </si>
+  <si>
+    <t>N7: SELECT from RunFiles. N8: Stream file from storage with Content-Disposition header.</t>
+  </si>
+  <si>
+    <t>Implement section129-run-status GET (N10) — polling endpoint</t>
+  </si>
+  <si>
+    <t>Return current StatusID + progress%. Frontend polls every 5s. Critical for UX during long-running jobs.</t>
+  </si>
+  <si>
+    <t>Implement section129-delete-run POST (N9) — soft delete draft runs</t>
+  </si>
+  <si>
+    <t>Only allow when StatusID=0. Soft delete (mark inactive, do not hard delete).</t>
+  </si>
+  <si>
+    <t>Implement section129-report GET (R1) — aggregated report query</t>
+  </si>
+  <si>
+    <t>Aggregate query across runs with date/town/status filters.</t>
+  </si>
+  <si>
+    <t>Implement sms-log-report GET (R2) — SMS delivery log</t>
+  </si>
+  <si>
+    <t>Read from SMS log table with status/date filters.</t>
+  </si>
+  <si>
+    <t>Service Bus</t>
+  </si>
+  <si>
+    <t>Create Azure Service Bus queue: section129-trial-run</t>
+  </si>
+  <si>
+    <t>Infra Team</t>
+  </si>
+  <si>
+    <t>Queue for background trial run processing. Worker reads message, queries qualifying accounts, writes results.</t>
+  </si>
+  <si>
+    <t>Create Azure Service Bus queue: section129-final-run</t>
+  </si>
+  <si>
+    <t>Queue for background PDF generation. Worker reads message, generates letters, writes files.</t>
+  </si>
+  <si>
+    <t>Create Trial Run Worker — background processor for account qualification</t>
+  </si>
+  <si>
+    <t>Reads from queue, applies qualification rules (ageing, amount, exclusions), writes qualifying accounts to Details table, updates StatusID=2.</t>
+  </si>
+  <si>
+    <t>Create Final Run Worker — background processor for notice generation</t>
+  </si>
+  <si>
+    <t>Reads from queue, generates PDF letters + SMS, writes to RunFiles table, updates StatusID=7.</t>
+  </si>
+  <si>
+    <t>Frontend</t>
+  </si>
+  <si>
+    <t>Verify all Angular components call correct /api/platinum/billing-debt/... paths</t>
+  </si>
+  <si>
+    <t>POS Team</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Verified and updated in codebase.</t>
+  </si>
+  <si>
+    <t>Verify TypeScript models match API response shapes (debt.models.ts)</t>
+  </si>
+  <si>
+    <t>Section129Run, Section129RunAccount, Section129Config updated to match API contracts.</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Integration test when APIs deployed to Swagger</t>
+  </si>
+  <si>
+    <t>Blocked</t>
+  </si>
+  <si>
+    <t>Cannot proceed until API team deploys endpoints to UAT Swagger.</t>
+  </si>
+  <si>
+    <t>Signoff</t>
+  </si>
+  <si>
+    <t>DBA reviews and signs off SQL change script before UAT deployment</t>
+  </si>
+  <si>
+    <t>DBA Lead</t>
+  </si>
+  <si>
+    <t>Must review PHASE1_V2_DB_CHANGE_SCRIPT.sql and approve.</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -144,6 +1332,183 @@
     <t>Angular Pages</t>
   </si>
   <si>
+    <t>Phase 0</t>
+  </si>
+  <si>
+    <t>Foundation &amp; Lookups</t>
+  </si>
+  <si>
+    <t>Lookup tables, shared filters, BillingDebt controller setup, database schema changes</t>
+  </si>
+  <si>
+    <t>4 ALTER TABLE, 4 new tables, 6 indexes, 10 lookup APIs, dropdown data</t>
+  </si>
+  <si>
+    <t>DBA approval, API controller creation</t>
+  </si>
+  <si>
+    <t>DESIGN COMPLETE</t>
+  </si>
+  <si>
+    <t>4 new + 4 ALTER</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>(shared across)</t>
+  </si>
+  <si>
+    <t>Phase 1</t>
+  </si>
+  <si>
+    <t>Section 129 Notices</t>
+  </si>
+  <si>
+    <t>S129 Config, Trial Run, Trial Review, Authorization, Final Run, Reports, SMS Log</t>
+  </si>
+  <si>
+    <t>Config CRUD, run lifecycle (Draft→Trial→Review→Approve→Final), file generation, polling, reports</t>
+  </si>
+  <si>
+    <t>Phase 0 tables + APIs, Azure Service Bus queues, Trial+Final workers</t>
+  </si>
+  <si>
+    <t>(uses Phase 0)</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Phase 2</t>
+  </si>
+  <si>
+    <t>Handover Management</t>
+  </si>
+  <si>
+    <t>Handover submit (account/bulk/rotation), Handover termination with audit, Handover reports, Attorney allocation</t>
+  </si>
+  <si>
+    <t>Handover lifecycle, termination workflow, handover reporting</t>
+  </si>
+  <si>
+    <t>Phase 1 (lapsed accounts feed into handover queue)</t>
+  </si>
+  <si>
+    <t>NOT STARTED</t>
+  </si>
+  <si>
+    <t>0 new (uses existing Cons_Handovers)</t>
+  </si>
+  <si>
+    <t>5+</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Phase 3</t>
+  </si>
+  <si>
+    <t>Risk Scoring &amp; Qualification</t>
+  </si>
+  <si>
+    <t>Risk scoring engine, Qualification rules CRUD, Bulk scoring, Scoring weight management</t>
+  </si>
+  <si>
+    <t>Score individual accounts, manage scoring weights, qualification rules engine, bulk qualification run</t>
+  </si>
+  <si>
+    <t>Phase 0 lookups</t>
+  </si>
+  <si>
+    <t>0 new (API-side tables)</t>
+  </si>
+  <si>
+    <t>10+</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Phase 4</t>
+  </si>
+  <si>
+    <t>Communication &amp; Batch</t>
+  </si>
+  <si>
+    <t>Communication timeline, Communication dashboard, Batch processing management, Process monitoring dashboard</t>
+  </si>
+  <si>
+    <t>Multi-channel comms (SMS/email/WhatsApp), batch job scheduling, monitoring/alerts</t>
+  </si>
+  <si>
+    <t>Phase 1 (S129 comms), Service Bus infrastructure</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>8+</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Phase 5</t>
+  </si>
+  <si>
+    <t>Legal Compliance</t>
+  </si>
+  <si>
+    <t>Legal rules CRUD, Audit trail viewer, Evidence bundles, Legal action validation</t>
+  </si>
+  <si>
+    <t>Compliance rules management, audit log, evidence bundle assembly</t>
+  </si>
+  <si>
+    <t>Phase 1-2 (auditable debt actions)</t>
+  </si>
+  <si>
+    <t>Phase 6</t>
+  </si>
+  <si>
+    <t>Documents &amp; Signatures</t>
+  </si>
+  <si>
+    <t>Document template management, Digital signature capture, Lapse tracker (14 workday monitoring)</t>
+  </si>
+  <si>
+    <t>Template CRUD, signature workflow, workday lapse monitoring</t>
+  </si>
+  <si>
+    <t>Phase 1 (S129 documents/notices)</t>
+  </si>
+  <si>
+    <t>6+</t>
+  </si>
+  <si>
+    <t>Phase 7</t>
+  </si>
+  <si>
+    <t>Process Engine &amp; Analytics</t>
+  </si>
+  <si>
+    <t>Process engine orchestration, Debt enquiry tab integration, Executive analytics dashboard</t>
+  </si>
+  <si>
+    <t>Process workflow orchestration, debt tabs in enquiries, analytics/forecasting</t>
+  </si>
+  <si>
+    <t>All prior phases</t>
+  </si>
+  <si>
+    <t>3+</t>
+  </si>
+  <si>
     <t>Used In Phase</t>
   </si>
   <si>
@@ -154,13 +1519,151 @@
   </si>
   <si>
     <t>Action Required</t>
+  </si>
+  <si>
+    <t>S129 run header — stores each trial/final run with metadata</t>
+  </si>
+  <si>
+    <t>ID, FinYear, FinMonth, RunType, BillingCycleID, HandoverOption, DistributionType, TownID, Ageing, AmountGreaterThan, IncludeIndigents, IncludePensioners (NEW), WhatsApp (NEW), StatusID (NEW), CapturerID, DateCaptured, ModifierID, DateModified</t>
+  </si>
+  <si>
+    <t>ALTER (add 3 columns)</t>
+  </si>
+  <si>
+    <t>Account-level results per S129 run — one row per qualifying account</t>
+  </si>
+  <si>
+    <t>DetailID, RunID (FK), AccountNo, AccountName, TotalBalance, CurrentBalance, BalanceDue, ThirtyDays, SixtyDays, NinetyDays, OverNinety, Selected (NEW)</t>
+  </si>
+  <si>
+    <t>ALTER (add 1 column)</t>
+  </si>
+  <si>
+    <t>Billing_Handover</t>
+  </si>
+  <si>
+    <t>Basic handover status flags on consumer accounts</t>
+  </si>
+  <si>
+    <t>HandoverStatus, ActivateDate</t>
+  </si>
+  <si>
+    <t>READ only</t>
+  </si>
+  <si>
+    <t>Cons_Handovers</t>
+  </si>
+  <si>
+    <t>Detailed handover records with attorney assignment and termination info</t>
+  </si>
+  <si>
+    <t>HandoverID, AttorneyID, AccountNo, HandoverDate, Amount, Status, TerminationDate, TerminationReason, CapturerID, DateCaptured</t>
+  </si>
+  <si>
+    <t>READ/WRITE via API</t>
+  </si>
+  <si>
+    <t>Cons_Handovers_Transactions</t>
+  </si>
+  <si>
+    <t>Financial breakdown of handed-over amounts by service type</t>
+  </si>
+  <si>
+    <t>TransactionID, HandoverID, ServiceType, Amount, DateCaptured</t>
+  </si>
+  <si>
+    <t>Const_Attorney</t>
+  </si>
+  <si>
+    <t>0/1/2</t>
+  </si>
+  <si>
+    <t>Attorney master data — name, contact, commission rates</t>
+  </si>
+  <si>
+    <t>ID, Name, ContactNo, Email, Commission</t>
+  </si>
+  <si>
+    <t>Billing_LetterTemplates</t>
+  </si>
+  <si>
+    <t>Document template storage for notices and letters</t>
+  </si>
+  <si>
+    <t>ID, TemplateName, TemplateType, Content, IsActive</t>
+  </si>
+  <si>
+    <t>Billing_LetterTypes</t>
+  </si>
+  <si>
+    <t>Notice type lookups (Section 129, Final Demand, etc.)</t>
+  </si>
+  <si>
+    <t>ID, TypeName</t>
+  </si>
+  <si>
+    <t>Billing_SelectedTemplates</t>
+  </si>
+  <si>
+    <t>Mapping between notice types and specific document templates</t>
+  </si>
+  <si>
+    <t>ID, LetterTypeID, TemplateID</t>
+  </si>
+  <si>
+    <t>Billing_BillingCycles</t>
+  </si>
+  <si>
+    <t>Billing cycle lookup for dropdown filters</t>
+  </si>
+  <si>
+    <t>ID, CycleName, CycleDescription</t>
+  </si>
+  <si>
+    <t>Const_Town</t>
+  </si>
+  <si>
+    <t>Town/area lookup for geographic filtering</t>
+  </si>
+  <si>
+    <t>ID, TownName</t>
+  </si>
+  <si>
+    <t>Const_PropertyCategory</t>
+  </si>
+  <si>
+    <t>Property category lookup (Residential, Commercial, etc.)</t>
+  </si>
+  <si>
+    <t>ID, CategoryName</t>
+  </si>
+  <si>
+    <t>Const_AccountType</t>
+  </si>
+  <si>
+    <t>Account type lookup (Owner, Tenant, Institution, etc.)</t>
+  </si>
+  <si>
+    <t>Const_TypeOfPerson</t>
+  </si>
+  <si>
+    <t>Person type lookup (Individual, Company, Trust, etc.)</t>
+  </si>
+  <si>
+    <t>Const_OutstandingPeriod</t>
+  </si>
+  <si>
+    <t>Ageing range lookup for debt age filtering</t>
+  </si>
+  <si>
+    <t>ID, PeriodName, DaysFrom, DaysTo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -170,11 +1673,16 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,7 +1691,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0F2B46"/>
+        <fgColor rgb="FF0F2B46"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -197,16 +1710,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </left>
       <right style="thin">
-        <color rgb="D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </right>
       <top style="thin">
-        <color rgb="D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="D1D5DB"/>
+        <color rgb="FFD1D5DB"/>
       </bottom>
       <diagonal/>
     </border>
@@ -214,10 +1727,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,10 +2077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="0F2B46"/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -612,6 +2128,1091 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -620,10 +3221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="C9A84C"/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -640,40 +3238,990 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>21</v>
+      <c r="C2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -684,10 +4232,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="22C55E"/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -697,7 +4242,7 @@
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="55" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -705,25 +4250,181 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>313</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>314</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>315</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>316</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -734,46 +4435,823 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="EF4444"/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="45" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>34</v>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -784,10 +5262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="8B5CF6"/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -803,28 +5278,260 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>431</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>432</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>433</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>434</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>317</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>435</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>436</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -835,17 +5542,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="64748B"/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="55" customWidth="1"/>
-    <col min="4" max="4" width="60" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -853,16 +5557,271 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>497</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>498</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>499</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>510</v>
       </c>
     </row>
   </sheetData>
